--- a/public/templates/Project_Setup_Template.xlsx
+++ b/public/templates/Project_Setup_Template.xlsx
@@ -69,13 +69,13 @@
     <t>Sales Owner</t>
   </si>
   <si>
-    <t>John Kunnath</t>
+    <t>Not yet tracked</t>
   </si>
   <si>
     <t>Project Manager</t>
   </si>
   <si>
-    <t>Suraj Rao</t>
+    <t>Not yet tracked</t>
   </si>
   <si>
     <t xml:space="preserve">  COMMERCIAL DETAILS</t>
